--- a/stories/arbres/ATOM-JEU.REG.002-07.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Isidore est au jardin avec maman. Un cerceau est au sol. Maman dit une règle. La règle : on attend. Puis on passe le cerceau. Isidore tend la main. Maman va rappeler la règle une fois. Elle dit : on attend. C'est la règle. Isidore attend. Puis il passe le cerceau. Maman dit : tu as suivi la règle. Isidore répète : une règle. Maman la rappelle. Isidore la suit.</t>
+          <t>Isidore est au jardin avec maman. Un cerceau est au sol. Maman dit une règle. La règle : on attend. Puis on passe le cerceau. Isidore tend la main. Maman va rappeler la règle une fois. On attend. C'est la règle. Isidore attend. Puis il passe le cerceau. Tu as suivi la règle. Isidore répète : une règle. Maman la rappelle. Isidore la suit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Isidore est au jardin avec maman. Un cerceau est au sol. Maman dit une règle. La règle : on attend. Puis on passe le cerceau. Isidore tend la main. Maman va rappeler la règle une fois.
+narrateur|On attend. C'est la règle.
+narrateur|Isidore attend. Puis il passe le cerceau.
+maman|Tu as suivi la règle.
+narrateur|Isidore répète : une règle. Maman la rappelle. Isidore la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Isidore joue. Que suit-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Isidore a suivi la règle. Maman l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le cerceau. Isidore donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-07.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Isidore répète : une règle. Maman la rappelle. Isidore la suit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Isidore joue. Que suit-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Isidore a suivi la règle. Maman l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Maman range le cerceau. Isidore donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.002-07.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Isidore suit la règle du cerceau</t>
+          <t>Le cerceau à ruban de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Près de la menthe, Sarah attend, puis passe le cerceau à ruban. Maman rappelle la règle une fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Isidore est au jardin avec maman. Un cerceau est au sol. Maman dit une règle. La règle : on attend. Puis on passe le cerceau. Isidore tend la main. Maman va rappeler la règle une fois. On attend. C'est la règle. Isidore attend. Puis il passe le cerceau. Tu as suivi la règle. Isidore répète : une règle. Maman la rappelle. Isidore la suit.</t>
+          <t>La menthe sent fort, près du muret. Un ruban rose pend au cerceau. Le linge sèche un peu plus loin. Une feuille de menthe brille au soleil. Le cerceau est lisse, un peu chaud. Une abeille va vers la menthe, puis s'en va. La terre du muret est sèche et claire. Le ruban bouge dans l'air. Un arrosoir bleu attend près du muret. Il a un peu d'eau au fond. L'eau tremble quand le vent passe. Tu as senti la menthe, Sarah ? Oui, maman. Elle pique un peu le nez. En ce moment, maman pose le cerceau. Le ruban frôle l'herbe. Une règle. On attend. Puis on passe le cerceau. J'ai envie de passer. On attend. Je te la rappelle une fois. C'est la règle. Sarah attend, les mains sur les genoux. Puis elle passe le cerceau. Le ruban glisse contre sa manche. Il chatouille. Tu as suivi la règle. Tu as attendu. Bravo, Sarah. On attend. Puis on passe le cerceau. Oui. Une règle simple. Je la rappelle une fois. Sarah attend encore. Puis elle passe le cerceau. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. La menthe sent encore, tout près. Le linge bouge un peu. Encore une fois, tout doux ? Oui, maman. Sarah attend. Puis elle passe le cerceau. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le ruban rose repose dans l'herbe. On range le cerceau après, d'accord ? D'accord. J'ai attendu. Sarah froisse une feuille de menthe. Elle sent fort, hein ? Oui. Elle pique. On attend, puis on passe. Bravo. Le ruban rose a un peu d'herbe. L'arrosoir reste près du muret. Le linge est presque sec. Il sent le savon. Oui. Une règle. On attend. Sarah pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Isidore est au jardin avec maman. Un cerceau est au sol. Maman dit une règle. La règle : on attend. Puis on passe le cerceau. Isidore tend la main. Maman va rappeler la règle une fois.
-narrateur|On attend. C'est la règle.
-narrateur|Isidore attend. Puis il passe le cerceau.
+          <t>narrateur|La menthe sent fort, près du muret.
+narrateur|Un ruban rose pend au cerceau.
+narrateur|Le linge sèche un peu plus loin.
+narrateur|Une feuille de menthe brille au soleil.
+narrateur|Le cerceau est lisse, un peu chaud.
+narrateur|Une abeille va vers la menthe, puis s'en va.
+narrateur|La terre du muret est sèche et claire.
+narrateur|Le ruban bouge dans l'air.
+narrateur|Un arrosoir bleu attend près du muret.
+narrateur|Il a un peu d'eau au fond.
+narrateur|L'eau tremble quand le vent passe.
+maman|Tu as senti la menthe, Sarah ?
+enfant-f|Oui, maman. Elle pique un peu le nez.
+narrateur|En ce moment, maman pose le cerceau.
+narrateur|Le ruban frôle l'herbe.
+maman|Une règle. On attend.
+maman|Puis on passe le cerceau.
+enfant-f|J'ai envie de passer.
+maman|On attend. Je te la rappelle une fois.
+maman|C'est la règle.
+narrateur|Sarah attend, les mains sur les genoux.
+narrateur|Puis elle passe le cerceau.
+narrateur|Le ruban glisse contre sa manche.
+enfant-f|Il chatouille.
 maman|Tu as suivi la règle.
-narrateur|Isidore répète : une règle. Maman la rappelle. Isidore la suit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Tu as attendu. Bravo, Sarah.
+enfant-f|On attend. Puis on passe le cerceau.
+maman|Oui. Une règle simple.
+maman|Je la rappelle une fois.
+narrateur|Sarah attend encore.
+narrateur|Puis elle passe le cerceau.
+maman|Tu as suivi la règle dite.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Une règle. On attend.
+maman|Oui. On la rappelle. Tu la suis.
+narrateur|La menthe sent encore, tout près.
+narrateur|Le linge bouge un peu.
+maman|Encore une fois, tout doux ?
+enfant-f|Oui, maman.
+narrateur|Sarah attend.
+narrateur|Puis elle passe le cerceau.
+maman|Bravo. Tu as attendu.
+enfant-f|J'ai suivi la règle.
+maman|Oui. Une règle. On la rappelle.
+narrateur|Le ruban rose repose dans l'herbe.
+maman|On range le cerceau après, d'accord ?
+enfant-f|D'accord. J'ai attendu.
+narrateur|Sarah froisse une feuille de menthe.
+maman|Elle sent fort, hein ?
+enfant-f|Oui. Elle pique.
+maman|On attend, puis on passe. Bravo.
+narrateur|Le ruban rose a un peu d'herbe.
+narrateur|L'arrosoir reste près du muret.
+maman|Le linge est presque sec.
+enfant-f|Il sent le savon.
+maman|Oui. Une règle. On attend.
+narrateur|Sarah pose les deux mains sur les genoux.
+narrateur|Elle attend. Puis elle passe.
+maman|Bravo. Tu as suivi la règle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Isidore joue. Que suit-il ?</t>
+          <t>Sarah joue. Que suit-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Isidore joue. Que suit-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah joue.
+narrateur|Que suit-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Isidore a suivi la règle. Maman l'a rappelée.</t>
+          <t>Sarah a suivi la règle. Maman l'a rappelée. Tu as attendu, puis tu as passé ? Oui. Une règle. Bravo. On la rappelle, et on la suit. Le ruban rose reste dans l'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,10 +1737,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Isidore a suivi la règle. Maman l'a rappelée.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a suivi la règle.
+narrateur|Maman l'a rappelée.
+maman|Tu as attendu, puis tu as passé ?
+enfant-f|Oui. Une règle.
+maman|Bravo. On la rappelle, et on la suit.
+narrateur|Le ruban rose reste dans l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le cerceau. Isidore donne la main.</t>
+          <t>On range le cerceau ? Oui, maman. Maman range le cerceau près du muret. Sarah donne la main. On va sentir la menthe encore ? Oui. Elle pique le nez. Le linge sèche encore un peu. L'arrosoir, on le laisse ? Oui. Il a de l'eau. Le ruban ne bouge plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1909,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le cerceau. Isidore donne la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>maman|On range le cerceau ?
+enfant-f|Oui, maman.
+narrateur|Maman range le cerceau près du muret.
+narrateur|Sarah donne la main.
+maman|On va sentir la menthe encore ?
+enfant-f|Oui. Elle pique le nez.
+narrateur|Le linge sèche encore un peu.
+maman|L'arrosoir, on le laisse ?
+enfant-f|Oui. Il a de l'eau.
+narrateur|Le ruban ne bouge plus.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1945,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille de menthe reste collée au doigt. J'ai attendu. Puis j'ai passé. Oui. Tu as suivi la règle. Bravo, Sarah. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,10 +2085,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Une feuille de menthe reste collée au doigt.
+enfant-f|J'ai attendu. Puis j'ai passé.
+maman|Oui. Tu as suivi la règle.
+maman|Bravo, Sarah.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-07.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La menthe sent fort, près du muret. Un ruban rose pend au cerceau. Le linge sèche un peu plus loin. Une feuille de menthe brille au soleil. Le cerceau est lisse, un peu chaud. Une abeille va vers la menthe, puis s'en va. La terre du muret est sèche et claire. Le ruban bouge dans l'air. Un arrosoir bleu attend près du muret. Il a un peu d'eau au fond. L'eau tremble quand le vent passe. Tu as senti la menthe, Sarah ? Oui, maman. Elle pique un peu le nez. En ce moment, maman pose le cerceau. Le ruban frôle l'herbe. Une règle. On attend. Puis on passe le cerceau. J'ai envie de passer. On attend. Je te la rappelle une fois. C'est la règle. Sarah attend, les mains sur les genoux. Puis elle passe le cerceau. Le ruban glisse contre sa manche. Il chatouille. Tu as suivi la règle. Tu as attendu. Bravo, Sarah. On attend. Puis on passe le cerceau. Oui. Une règle simple. Je la rappelle une fois. Sarah attend encore. Puis elle passe le cerceau. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. La menthe sent encore, tout près. Le linge bouge un peu. Encore une fois, tout doux ? Oui, maman. Sarah attend. Puis elle passe le cerceau. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le ruban rose repose dans l'herbe. On range le cerceau après, d'accord ? D'accord. J'ai attendu. Sarah froisse une feuille de menthe. Elle sent fort, hein ? Oui. Elle pique. On attend, puis on passe. Bravo. Le ruban rose a un peu d'herbe. L'arrosoir reste près du muret. Le linge est presque sec. Il sent le savon. Oui. Une règle. On attend. Sarah pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
+          <t>La menthe sent fort, près du muret. Un ruban rose pend au cerceau. Le linge sèche un peu plus loin. Une feuille de menthe brille au soleil. Le cerceau est lisse, un peu chaud. Une abeille va vers la menthe, puis s'en va. La terre du muret est sèche et claire. Le ruban bouge dans l'air. Un arrosoir bleu attend près du muret. Il a un peu d'eau au fond. L'eau tremble quand le vent passe. Tu as senti la menthe, Sarah ? Oui, maman. Elle pique un peu le nez. En ce moment, maman pose le cerceau. Le ruban frôle l'herbe. Une règle. On attend. Puis on passe le cerceau. J'ai envie de passer. On attend. Je te la rappelle une fois. C'est la règle. Sarah attend, les mains sur les genoux. Puis elle passe le cerceau. Le ruban glisse contre sa manche. Il chatouille. Tu as suivi la règle. Tu as attendu. Bravo, Sarah. On attend. Puis on passe le cerceau. Oui. Une règle simple. Je la rappelle une fois. Sarah attend encore. Puis elle passe le cerceau. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. La menthe sent encore, tout près. Le linge bouge un peu. Encore une fois, tout doux ? Oui, maman. Sarah attend. Puis elle passe le cerceau. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le ruban rose repose dans l'herbe. On range le cerceau après, d'accord ? D'accord. J'ai attendu. Sarah froisse une feuille de menthe. Elle sent fort, hein ? Oui. Elle pique. On attend, puis on passe. Bravo. Le ruban rose a un peu d'herbe. L'arrosoir reste près du muret. Le linge est presque sec. Il sent le savon. Oui. Une règle. On attend. Sarah pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Isidore est au jardin avec maman. Un cerceau est au sol. Maman dit &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; règle. La règle : on attend. Puis on passe le cerceau. Isidore tend la main. Maman va rappeler la règle une fois. Elle dit : on attend. C'est la règle. Isidore attend. Puis il passe le cerceau. Maman dit : tu as suivi la règle. Isidore répète : une règle. Maman la rappelle. Isidore la suit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La menthe sent fort, près du muret. Un ruban rose pend au cerceau. Le linge sèche un peu plus loin. Une feuille de menthe brille au soleil. Le cerceau est lisse, un peu chaud. Une abeille va vers la menthe, puis s'en va. La terre du muret est sèche et claire. Le ruban bouge dans l'air. Un arrosoir bleu attend près du muret. Il a un peu d'eau au fond. L'eau tremble quand le vent passe. Tu as senti la menthe, Sarah ? Oui, maman. Elle pique un peu le nez. En ce moment, maman pose le cerceau. Le ruban frôle l'herbe. Une règle. On attend. Puis on passe le cerceau. J'ai envie de passer. On attend. Je te la rappelle une fois. C'est la règle. Sarah attend, les mains sur les genoux. Puis elle passe le cerceau. Le ruban glisse contre sa manche. Il chatouille. Tu as suivi la règle. Tu as attendu. Bravo, Sarah. On attend. Puis on passe le cerceau. Oui. Une règle simple. Je la rappelle une fois. Sarah attend encore. Puis elle passe le cerceau. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. La menthe sent encore, tout près. Le linge bouge un peu. Encore une fois, tout doux ? Oui, maman. Sarah attend. Puis elle passe le cerceau. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le ruban rose repose dans l'herbe. On range le cerceau après, d'accord ? D'accord. J'ai attendu. Sarah froisse une feuille de menthe. Elle sent fort, hein ? Oui. Elle pique. On attend, puis on passe. Bravo. Le ruban rose a un peu d'herbe. L'arrosoir reste près du muret. Le linge est presque sec. Il sent le savon. Oui. Une règle. On attend. Sarah pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1356,7 +1356,6 @@
 narrateur|Sarah attend encore.
 narrateur|Puis elle passe le cerceau.
 maman|Tu as suivi la règle dite.
-maman|Bravo. Tu as fait du bon travail.
 enfant-f|Une règle. On attend.
 maman|Oui. On la rappelle. Tu la suis.
 narrateur|La menthe sent encore, tout près.
@@ -1414,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Isidore joue. Que suit-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah joue. Que suit-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1598,7 +1597,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Isidore a suivi &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; règle. Maman l'a rappelée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a suivi la règle. Maman l'a rappelée. Tu as attendu, puis tu as passé ? Oui. Une règle. Bravo. On la rappelle, et on la suit. Le ruban rose reste dans l'herbe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1774,7 +1773,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le cerceau. Isidore donne &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range le cerceau ? Oui, maman. Maman range le cerceau près du muret. Sarah donne la main. On va sentir la menthe encore ? Oui. Elle pique le nez. Le linge sèche encore un peu. L'arrosoir, on le laisse ? Oui. Il a de l'eau. Le ruban ne bouge plus.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Une feuille de menthe reste collée au doigt. J'ai attendu. Puis j'ai passé. Oui. Tu as suivi la règle. Bravo, Sarah. L'histoire est finie.</t>
+          <t>Une feuille de menthe reste collée au doigt. J'ai attendu. Puis j'ai passé. Oui. Tu as suivi la règle. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille de menthe reste collée au doigt. J'ai attendu. Puis j'ai passé. Oui. Tu as suivi la règle. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2088,8 +2087,7 @@
           <t>narrateur|Une feuille de menthe reste collée au doigt.
 enfant-f|J'ai attendu. Puis j'ai passé.
 maman|Oui. Tu as suivi la règle.
-maman|Bravo, Sarah.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Sarah.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2155,6 +2153,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-07.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, pied de menthe, cerceau à ruban, linge</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Isidore, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-07.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-07.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le cerceau à ruban de Sarah</t>
+          <t>Le cerceau des poules</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin, pied de menthe, cerceau à ruban, linge</t>
+          <t>cour de ferme, puits, soir d'été</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sarah, maman</t>
+          <t>Victorino, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Près de la menthe, Sarah attend, puis passe le cerceau à ruban. Maman rappelle la règle une fois.</t>
+          <t>Victorino veut passer dans le cerceau vert de la ferme. Il pousse trop tôt, le cerceau tombe, le grain s'éparpille, la poule a peur. Ils attendent un peu. Maman tient, il passe. La poule picore, le soir est orange.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La menthe sent fort, près du muret. Un ruban rose pend au cerceau. Le linge sèche un peu plus loin. Une feuille de menthe brille au soleil. Le cerceau est lisse, un peu chaud. Une abeille va vers la menthe, puis s'en va. La terre du muret est sèche et claire. Le ruban bouge dans l'air. Un arrosoir bleu attend près du muret. Il a un peu d'eau au fond. L'eau tremble quand le vent passe. Tu as senti la menthe, Sarah ? Oui, maman. Elle pique un peu le nez. En ce moment, maman pose le cerceau. Le ruban frôle l'herbe. Une règle. On attend. Puis on passe le cerceau. J'ai envie de passer. On attend. Je te la rappelle une fois. C'est la règle. Sarah attend, les mains sur les genoux. Puis elle passe le cerceau. Le ruban glisse contre sa manche. Il chatouille. Tu as suivi la règle. Tu as attendu. Bravo, Sarah. On attend. Puis on passe le cerceau. Oui. Une règle simple. Je la rappelle une fois. Sarah attend encore. Puis elle passe le cerceau. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. La menthe sent encore, tout près. Le linge bouge un peu. Encore une fois, tout doux ? Oui, maman. Sarah attend. Puis elle passe le cerceau. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le ruban rose repose dans l'herbe. On range le cerceau après, d'accord ? D'accord. J'ai attendu. Sarah froisse une feuille de menthe. Elle sent fort, hein ? Oui. Elle pique. On attend, puis on passe. Bravo. Le ruban rose a un peu d'herbe. L'arrosoir reste près du muret. Le linge est presque sec. Il sent le savon. Oui. Une règle. On attend. Sarah pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
+          <t>Une poule rousse picore près du cerceau. La cour de la ferme sent le foin chaud. Le mur de pierre est encore tiède. Le soir descend, tout orange. Un seau de grain cliquette, un peu. Le cerceau vert est posé contre le puits. Victorino, tu vois le cerceau ? Oui, maman. Je veux passer. Maman prend déjà le cerceau. Elle n'a pas encore les deux mains. En ce moment, Victorino court. Comme un tunnel. J'ai pas encore tenu. Victorino pousse le cerceau trop vite. Le cerceau tombe. Il tape le seau. Le grain s'éparpille. La poule rousse s'envole, tout bas. Oh. Elle a peur. Le jeu s'est arrêté. On attend un peu ? Victorino s'arrête près du puits. La pierre est rêche sous la main. Ça sent le grain, tout fort. Je ramasse le grain ? Oui. Pour la poule, tout doux. Il ramasse des grains, un par un. Ils sont secs, un peu ronds. La poule revient, la tête penchée. Elle est là. Elle attend, elle aussi. Maman tient le cerceau, cette fois. Ses deux mains sont dessus. Tu attends que je sois prête ? Oui. On attend un peu. Victorino reste les pieds dans la poussière. Il regarde le trou vert. La poule picore, tout calme. Le mur orange tient la chaleur.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La menthe sent fort, près du muret. Un ruban rose pend au cerceau. Le linge sèche un peu plus loin. Une feuille de menthe brille au soleil. Le cerceau est lisse, un peu chaud. Une abeille va vers la menthe, puis s'en va. La terre du muret est sèche et claire. Le ruban bouge dans l'air. Un arrosoir bleu attend près du muret. Il a un peu d'eau au fond. L'eau tremble quand le vent passe. Tu as senti la menthe, Sarah ? Oui, maman. Elle pique un peu le nez. En ce moment, maman pose le cerceau. Le ruban frôle l'herbe. Une règle. On attend. Puis on passe le cerceau. J'ai envie de passer. On attend. Je te la rappelle une fois. C'est la règle. Sarah attend, les mains sur les genoux. Puis elle passe le cerceau. Le ruban glisse contre sa manche. Il chatouille. Tu as suivi la règle. Tu as attendu. Bravo, Sarah. On attend. Puis on passe le cerceau. Oui. Une règle simple. Je la rappelle une fois. Sarah attend encore. Puis elle passe le cerceau. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. La menthe sent encore, tout près. Le linge bouge un peu. Encore une fois, tout doux ? Oui, maman. Sarah attend. Puis elle passe le cerceau. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le ruban rose repose dans l'herbe. On range le cerceau après, d'accord ? D'accord. J'ai attendu. Sarah froisse une feuille de menthe. Elle sent fort, hein ? Oui. Elle pique. On attend, puis on passe. Bravo. Le ruban rose a un peu d'herbe. L'arrosoir reste près du muret. Le linge est presque sec. Il sent le savon. Oui. Une règle. On attend. Sarah pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
+          <t>Une poule rousse picore près du cerceau. La cour de la ferme sent le foin chaud. Le mur de pierre est encore tiède. Le soir descend, tout orange. Un seau de grain cliquette, un peu. Le cerceau vert est posé contre le puits. Victorino, tu vois le cerceau ? Oui, maman. Je veux passer. Maman prend déjà le cerceau. Elle n'a pas encore les deux mains. En ce moment, Victorino court. Comme un tunnel. J'ai pas encore tenu. Victorino pousse le cerceau trop vite. Le cerceau tombe. Il tape le seau. Le grain s'éparpille. La poule rousse s'envole, tout bas. Oh. Elle a peur. Le jeu s'est arrêté. On attend un peu ? Victorino s'arrête près du puits. La pierre est rêche sous la main. Ça sent le grain, tout fort. Je ramasse le grain ? Oui. Pour la poule, tout doux. Il ramasse des grains, un par un. Ils sont secs, un peu ronds. La poule revient, la tête penchée. Elle est là. Elle attend, elle aussi. Maman tient le cerceau, cette fois. Ses deux mains sont dessus. Tu attends que je sois prête ? Oui. On attend un peu. Victorino reste les pieds dans la poussière. Il regarde le trou vert. La poule picore, tout calme. Le mur orange tient la chaleur.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,64 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La menthe sent fort, près du muret.
-narrateur|Un ruban rose pend au cerceau.
-narrateur|Le linge sèche un peu plus loin.
-narrateur|Une feuille de menthe brille au soleil.
-narrateur|Le cerceau est lisse, un peu chaud.
-narrateur|Une abeille va vers la menthe, puis s'en va.
-narrateur|La terre du muret est sèche et claire.
-narrateur|Le ruban bouge dans l'air.
-narrateur|Un arrosoir bleu attend près du muret.
-narrateur|Il a un peu d'eau au fond.
-narrateur|L'eau tremble quand le vent passe.
-maman|Tu as senti la menthe, Sarah ?
-enfant-f|Oui, maman. Elle pique un peu le nez.
-narrateur|En ce moment, maman pose le cerceau.
-narrateur|Le ruban frôle l'herbe.
-maman|Une règle. On attend.
-maman|Puis on passe le cerceau.
-enfant-f|J'ai envie de passer.
-maman|On attend. Je te la rappelle une fois.
-maman|C'est la règle.
-narrateur|Sarah attend, les mains sur les genoux.
-narrateur|Puis elle passe le cerceau.
-narrateur|Le ruban glisse contre sa manche.
-enfant-f|Il chatouille.
-maman|Tu as suivi la règle.
-maman|Tu as attendu. Bravo, Sarah.
-enfant-f|On attend. Puis on passe le cerceau.
-maman|Oui. Une règle simple.
-maman|Je la rappelle une fois.
-narrateur|Sarah attend encore.
-narrateur|Puis elle passe le cerceau.
-maman|Tu as suivi la règle dite.
-enfant-f|Une règle. On attend.
-maman|Oui. On la rappelle. Tu la suis.
-narrateur|La menthe sent encore, tout près.
-narrateur|Le linge bouge un peu.
-maman|Encore une fois, tout doux ?
-enfant-f|Oui, maman.
-narrateur|Sarah attend.
-narrateur|Puis elle passe le cerceau.
-maman|Bravo. Tu as attendu.
-enfant-f|J'ai suivi la règle.
-maman|Oui. Une règle. On la rappelle.
-narrateur|Le ruban rose repose dans l'herbe.
-maman|On range le cerceau après, d'accord ?
-enfant-f|D'accord. J'ai attendu.
-narrateur|Sarah froisse une feuille de menthe.
-maman|Elle sent fort, hein ?
-enfant-f|Oui. Elle pique.
-maman|On attend, puis on passe. Bravo.
-narrateur|Le ruban rose a un peu d'herbe.
-narrateur|L'arrosoir reste près du muret.
-maman|Le linge est presque sec.
-enfant-f|Il sent le savon.
-maman|Oui. Une règle. On attend.
-narrateur|Sarah pose les deux mains sur les genoux.
-narrateur|Elle attend. Puis elle passe.
-maman|Bravo. Tu as suivi la règle.</t>
+          <t>narrateur|Une poule rousse picore près du cerceau.
+narrateur|La cour de la ferme sent le foin chaud.
+narrateur|Le mur de pierre est encore tiède.
+narrateur|Le soir descend, tout orange.
+narrateur|Un seau de grain cliquette, un peu.
+narrateur|Le cerceau vert est posé contre le puits.
+maman|Victorino, tu vois le cerceau ?
+enfant-m|Oui, maman.
+enfant-m|Je veux passer.
+narrateur|Maman prend déjà le cerceau.
+narrateur|Elle n'a pas encore les deux mains.
+narrateur|En ce moment, Victorino court.
+enfant-m|Comme un tunnel.
+maman|J'ai pas encore tenu.
+narrateur|Victorino pousse le cerceau trop vite.
+narrateur|Le cerceau tombe.
+narrateur|Il tape le seau.
+narrateur|Le grain s'éparpille.
+narrateur|La poule rousse s'envole, tout bas.
+enfant-m|Oh.
+enfant-m|Elle a peur.
+maman|Le jeu s'est arrêté.
+maman|On attend un peu ?
+narrateur|Victorino s'arrête près du puits.
+narrateur|La pierre est rêche sous la main.
+narrateur|Ça sent le grain, tout fort.
+enfant-m|Je ramasse le grain ?
+maman|Oui.
+maman|Pour la poule, tout doux.
+narrateur|Il ramasse des grains, un par un.
+narrateur|Ils sont secs, un peu ronds.
+narrateur|La poule revient, la tête penchée.
+enfant-m|Elle est là.
+maman|Elle attend, elle aussi.
+narrateur|Maman tient le cerceau, cette fois.
+narrateur|Ses deux mains sont dessus.
+maman|Tu attends que je sois prête ?
+enfant-m|Oui.
+maman|On attend un peu.
+narrateur|Victorino reste les pieds dans la poussière.
+narrateur|Il regarde le trou vert.
+narrateur|La poule picore, tout calme.
+narrateur|Le mur orange tient la chaleur.</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1393,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sarah joue. Que suit-elle ?</t>
+          <t>Victorino veut passer. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sarah joue. Que suit-elle ?</t>
+          <t>Victorino veut passer. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1423,12 +1408,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la règle</t>
+          <t>attendre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la règle | une règle | attendre</t>
+          <t>attendre | on attend | un peu | son tour | elle attend | il attend | attendre un peu | on attend un peu | à son tour</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1443,7 +1428,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Maman rappelle. Quelle chose Isidore suit ?</t>
+          <t>Il reste un peu. Que fait Victorino d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1485,14 +1470,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1564,8 +1549,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sarah joue.
-narrateur|Que suit-elle ?</t>
+          <t>narrateur|Victorino veut passer.
+narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a suivi la règle. Maman l'a rappelée. Tu as attendu, puis tu as passé ? Oui. Une règle. Bravo. On la rappelle, et on la suit. Le ruban rose reste dans l'herbe.</t>
+          <t>Victorino reste encore un peu. J'ai les deux mains. Tu peux passer. J'y vais. Il plie les genoux. Il passe dans le trou vert. Le cerceau ne tombe pas. Je suis passé ! Oui. Il est resté debout. La poule picore près du seau. Elle n'a plus peur. Encore une fois ? Encore. On attend un peu. Maman replace le cerceau. Victorino compte, sans courir. Un. Deux. Maintenant. Il passe encore. Ses cheveux touchent le plastique. Merci, Victorino. C'est un tunnel.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a suivi la règle. Maman l'a rappelée. Tu as attendu, puis tu as passé ? Oui. Une règle. Bravo. On la rappelle, et on la suit. Le ruban rose reste dans l'herbe.</t>
+          <t>Victorino reste encore un peu. J'ai les deux mains. Tu peux passer. J'y vais. Il plie les genoux. Il passe dans le trou vert. Le cerceau ne tombe pas. Je suis passé ! Oui. Il est resté debout. La poule picore près du seau. Elle n'a plus peur. Encore une fois ? Encore. On attend un peu. Maman replace le cerceau. Victorino compte, sans courir. Un. Deux. Maintenant. Il passe encore. Ses cheveux touchent le plastique. Merci, Victorino. C'est un tunnel.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1660,7 +1645,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1736,12 +1721,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a suivi la règle.
-narrateur|Maman l'a rappelée.
-maman|Tu as attendu, puis tu as passé ?
-enfant-f|Oui. Une règle.
-maman|Bravo. On la rappelle, et on la suit.
-narrateur|Le ruban rose reste dans l'herbe.</t>
+          <t>narrateur|Victorino reste encore un peu.
+maman|J'ai les deux mains.
+maman|Tu peux passer.
+enfant-m|J'y vais.
+narrateur|Il plie les genoux.
+narrateur|Il passe dans le trou vert.
+narrateur|Le cerceau ne tombe pas.
+enfant-m|Je suis passé !
+maman|Oui.
+maman|Il est resté debout.
+narrateur|La poule picore près du seau.
+narrateur|Elle n'a plus peur.
+maman|Encore une fois ?
+enfant-m|Encore.
+maman|On attend un peu.
+narrateur|Maman replace le cerceau.
+narrateur|Victorino compte, sans courir.
+narrateur|Un.
+narrateur|Deux.
+maman|Maintenant.
+narrateur|Il passe encore.
+narrateur|Ses cheveux touchent le plastique.
+maman|Merci, Victorino.
+enfant-m|C'est un tunnel.</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On range le cerceau ? Oui, maman. Maman range le cerceau près du muret. Sarah donne la main. On va sentir la menthe encore ? Oui. Elle pique le nez. Le linge sèche encore un peu. L'arrosoir, on le laisse ? Oui. Il a de l'eau. Le ruban ne bouge plus.</t>
+          <t>On donne le reste du grain ? Pour la poule. Victorino tend le poing, tout doux. Les grains tombent près des pattes. La poule picore, un grain, puis l'autre. Elle attend, elle aussi. Oui. Un peu, puis elle mange. Le cerceau vert attend contre le puits. Je repasse ? Oui. Quand je tiens bien. Ils reviennent près du mur tiède. Le soir est plus orange, maintenant. Victorino attend, les mains ouvertes. Tu es prêt ? Oui, maman. Il passe tout droit. Le plastique reste chaud. Une autre poule arrive, plus sombre. Elles regardent. Oui. Le jeu a repris.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On range le cerceau ? Oui, maman. Maman range le cerceau près du muret. Sarah donne la main. On va sentir la menthe encore ? Oui. Elle pique le nez. Le linge sèche encore un peu. L'arrosoir, on le laisse ? Oui. Il a de l'eau. Le ruban ne bouge plus.</t>
+          <t>On donne le reste du grain ? Pour la poule. Victorino tend le poing, tout doux. Les grains tombent près des pattes. La poule picore, un grain, puis l'autre. Elle attend, elle aussi. Oui. Un peu, puis elle mange. Le cerceau vert attend contre le puits. Je repasse ? Oui. Quand je tiens bien. Ils reviennent près du mur tiède. Le soir est plus orange, maintenant. Victorino attend, les mains ouvertes. Tu es prêt ? Oui, maman. Il passe tout droit. Le plastique reste chaud. Une autre poule arrive, plus sombre. Elles regardent. Oui. Le jeu a repris.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1836,7 +1839,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1908,16 +1911,29 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On range le cerceau ?
-enfant-f|Oui, maman.
-narrateur|Maman range le cerceau près du muret.
-narrateur|Sarah donne la main.
-maman|On va sentir la menthe encore ?
-enfant-f|Oui. Elle pique le nez.
-narrateur|Le linge sèche encore un peu.
-maman|L'arrosoir, on le laisse ?
-enfant-f|Oui. Il a de l'eau.
-narrateur|Le ruban ne bouge plus.</t>
+          <t>maman|On donne le reste du grain ?
+enfant-m|Pour la poule.
+narrateur|Victorino tend le poing, tout doux.
+narrateur|Les grains tombent près des pattes.
+narrateur|La poule picore, un grain, puis l'autre.
+enfant-m|Elle attend, elle aussi.
+maman|Oui.
+maman|Un peu, puis elle mange.
+narrateur|Le cerceau vert attend contre le puits.
+enfant-m|Je repasse ?
+maman|Oui.
+maman|Quand je tiens bien.
+narrateur|Ils reviennent près du mur tiède.
+narrateur|Le soir est plus orange, maintenant.
+narrateur|Victorino attend, les mains ouvertes.
+maman|Tu es prêt ?
+enfant-m|Oui, maman.
+narrateur|Il passe tout droit.
+narrateur|Le plastique reste chaud.
+narrateur|Une autre poule arrive, plus sombre.
+enfant-m|Elles regardent.
+maman|Oui.
+maman|Le jeu a repris.</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Une feuille de menthe reste collée au doigt. J'ai attendu. Puis j'ai passé. Oui. Tu as suivi la règle. Bravo, Sarah.</t>
+          <t>Le tunnel est vert au soir. Et toi, tu as attendu. Bravo, Victorino. Le foin sent encore, tout chaud. La poule rousse picore près du cerceau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Une feuille de menthe reste collée au doigt. J'ai attendu. Puis j'ai passé. Oui. Tu as suivi la règle. Bravo, Sarah.</t>
+          <t>Le tunnel est vert au soir. Et toi, tu as attendu. Bravo, Victorino. Le foin sent encore, tout chaud. La poule rousse picore près du cerceau.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2012,7 +2028,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2084,10 +2100,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Une feuille de menthe reste collée au doigt.
-enfant-f|J'ai attendu. Puis j'ai passé.
-maman|Oui. Tu as suivi la règle.
-maman|Bravo, Sarah.</t>
+          <t>enfant-m|Le tunnel est vert au soir.
+maman|Et toi, tu as attendu.
+maman|Bravo, Victorino.
+narrateur|Le foin sent encore, tout chaud.
+narrateur|La poule rousse picore près du cerceau.</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2158,6 +2175,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
